--- a/CPRD Raw Analysis/Results/Overall/overall_combined_summary_encounters_SOURCE.xlsx
+++ b/CPRD Raw Analysis/Results/Overall/overall_combined_summary_encounters_SOURCE.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L5"/>
+  <dimension ref="A1:L3"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -429,7 +429,7 @@
         <v>39.02</v>
       </c>
       <c r="D2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E2">
         <v>678</v>
@@ -459,121 +459,41 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>All Patients &amp; relevant encounters</t>
+          <t>Users &amp; all encounters</t>
         </is>
       </c>
       <c r="B3">
-        <v>23106</v>
+        <v>22478</v>
       </c>
       <c r="C3">
-        <v>23.05</v>
+        <v>40</v>
       </c>
       <c r="D3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E3">
-        <v>401</v>
+        <v>678</v>
       </c>
       <c r="F3">
-        <v>24.01</v>
+        <v>37.44</v>
       </c>
       <c r="G3">
-        <v>16</v>
+        <v>29</v>
       </c>
       <c r="H3">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="I3">
-        <v>31</v>
+        <v>52</v>
       </c>
       <c r="J3">
-        <v>0.16</v>
+        <v>0.25</v>
       </c>
       <c r="K3">
-        <v>22.74</v>
+        <v>39.51</v>
       </c>
       <c r="L3">
-        <v>23.36</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Users &amp; all encounters</t>
-        </is>
-      </c>
-      <c r="B4">
-        <v>22466</v>
-      </c>
-      <c r="C4">
-        <v>40.01</v>
-      </c>
-      <c r="D4">
-        <v>1</v>
-      </c>
-      <c r="E4">
-        <v>678</v>
-      </c>
-      <c r="F4">
-        <v>37.44</v>
-      </c>
-      <c r="G4">
-        <v>29</v>
-      </c>
-      <c r="H4">
-        <v>15</v>
-      </c>
-      <c r="I4">
-        <v>52</v>
-      </c>
-      <c r="J4">
-        <v>0.25</v>
-      </c>
-      <c r="K4">
-        <v>39.52</v>
-      </c>
-      <c r="L4">
-        <v>40.5</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Users &amp; relevant encounters</t>
-        </is>
-      </c>
-      <c r="B5">
-        <v>22466</v>
-      </c>
-      <c r="C5">
-        <v>23.71</v>
-      </c>
-      <c r="D5">
-        <v>1</v>
-      </c>
-      <c r="E5">
-        <v>401</v>
-      </c>
-      <c r="F5">
-        <v>24.02</v>
-      </c>
-      <c r="G5">
-        <v>17</v>
-      </c>
-      <c r="H5">
-        <v>8</v>
-      </c>
-      <c r="I5">
-        <v>32</v>
-      </c>
-      <c r="J5">
-        <v>0.16</v>
-      </c>
-      <c r="K5">
-        <v>23.39</v>
-      </c>
-      <c r="L5">
-        <v>24.02</v>
+        <v>40.49</v>
       </c>
     </row>
   </sheetData>
